--- a/data/trans_bre/P16A13-Provincia-trans_bre.xlsx
+++ b/data/trans_bre/P16A13-Provincia-trans_bre.xlsx
@@ -660,42 +660,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-2,41; 3,21</t>
+          <t>-2,42; 2,76</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-4,3; 4,57</t>
+          <t>-3,83; 4,78</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>1,43; 9,43</t>
+          <t>1,51; 9,45</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-7,68; 1,56</t>
+          <t>-7,93; 1,49</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-67,57; 262,52</t>
+          <t>-71,05; 197,11</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-51,73; 121,32</t>
+          <t>-45,5; 126,86</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>24,94; 620,05</t>
+          <t>20,35; 535,7</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-68,83; 41,38</t>
+          <t>-72,6; 35,48</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-2,0; 2,52</t>
+          <t>-1,86; 2,64</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-2,35; 3,97</t>
+          <t>-2,2; 3,84</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-2,12; 1,14</t>
+          <t>-2,26; 1,12</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-1,33; 2,84</t>
+          <t>-1,57; 2,58</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-42,97; 109,18</t>
+          <t>-39,46; 118,85</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-33,45; 103,62</t>
+          <t>-34,74; 96,67</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-70,24; 103,53</t>
+          <t>-70,0; 114,44</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-36,11; 198,64</t>
+          <t>-43,36; 172,96</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-0,29; 4,91</t>
+          <t>-0,03; 4,71</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-3,18; 3,47</t>
+          <t>-3,17; 3,4</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-2,25; 1,82</t>
+          <t>-1,95; 2,34</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>1,11; 9,43</t>
+          <t>0,96; 9,73</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-22,76; 809,03</t>
+          <t>-23,32; 676,7</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-58,71; 178,86</t>
+          <t>-60,79; 170,13</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-78,45; 197,09</t>
+          <t>-70,83; 313,8</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>6,87; 110,92</t>
+          <t>6,22; 111,78</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-0,24; 4,71</t>
+          <t>-0,22; 4,7</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>2,34; 9,05</t>
+          <t>2,54; 9,01</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-0,27; 7,16</t>
+          <t>-0,48; 7,33</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-2,73; 5,38</t>
+          <t>-2,51; 5,3</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-24,64; 502,03</t>
+          <t>-16,64; 485,35</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>53,79; 849,43</t>
+          <t>36,42; 792,98</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-10,22; 216,99</t>
+          <t>-11,22; 227,33</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-34,4; 117,08</t>
+          <t>-30,26; 116,99</t>
         </is>
       </c>
     </row>
@@ -1060,42 +1060,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-1,1; 5,6</t>
+          <t>-0,7; 5,86</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-6,12; 4,52</t>
+          <t>-6,27; 3,91</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-0,98; 5,02</t>
+          <t>-0,99; 5,06</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>2,53; 13,1</t>
+          <t>2,15; 13,0</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-52,6; 804,6</t>
+          <t>-48,52; 811,98</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-59,6; 94,04</t>
+          <t>-57,79; 73,53</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-61,63; —</t>
+          <t>-61,0; 948,38</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>13,55; 127,56</t>
+          <t>12,12; 117,04</t>
         </is>
       </c>
     </row>
@@ -1160,42 +1160,42 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-0,3; 5,44</t>
+          <t>-0,39; 5,4</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-5,15; 1,87</t>
+          <t>-5,03; 2,24</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-3,37; 2,09</t>
+          <t>-3,47; 2,09</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-2,65; 6,43</t>
+          <t>-2,51; 6,61</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-27,54; 588,87</t>
+          <t>-28,79; 717,37</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-69,51; 60,04</t>
+          <t>-66,21; 75,02</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-75,54; 169,2</t>
+          <t>-77,65; 143,03</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-16,22; 53,3</t>
+          <t>-14,69; 58,84</t>
         </is>
       </c>
     </row>
@@ -1260,42 +1260,42 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-0,69; 3,58</t>
+          <t>-0,73; 3,64</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-0,57; 4,19</t>
+          <t>-0,76; 4,34</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-1,31; 3,41</t>
+          <t>-1,37; 3,47</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-4,0; 3,58</t>
+          <t>-3,49; 3,83</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-18,98; 167,3</t>
+          <t>-21,33; 174,99</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-15,73; 149,32</t>
+          <t>-19,79; 167,37</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-30,01; 133,07</t>
+          <t>-29,25; 128,39</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-48,78; 68,66</t>
+          <t>-49,92; 75,73</t>
         </is>
       </c>
     </row>
@@ -1360,42 +1360,42 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-2,41; 0,83</t>
+          <t>-2,42; 0,76</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-0,43; 3,39</t>
+          <t>-0,66; 3,2</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-1,08; 2,56</t>
+          <t>-1,11; 2,52</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-1,34; 2,29</t>
+          <t>-1,32; 2,5</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-61,29; 42,13</t>
+          <t>-61,33; 39,81</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-15,8; 191,3</t>
+          <t>-20,34; 174,97</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-32,08; 145,51</t>
+          <t>-34,27; 133,97</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-35,15; 154,34</t>
+          <t>-34,03; 158,23</t>
         </is>
       </c>
     </row>
@@ -1460,42 +1460,42 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>0,17; 1,77</t>
+          <t>0,08; 1,82</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>0,14; 2,34</t>
+          <t>0,2; 2,36</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>0,11; 2,07</t>
+          <t>0,18; 1,95</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>0,09; 3,27</t>
+          <t>0,16; 3,36</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>4,84; 78,22</t>
+          <t>1,76; 85,31</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>2,78; 64,62</t>
+          <t>4,07; 66,76</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>2,88; 80,53</t>
+          <t>4,94; 77,86</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>2,49; 62,71</t>
+          <t>3,32; 67,03</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/P16A13-Provincia-trans_bre.xlsx
+++ b/data/trans_bre/P16A13-Provincia-trans_bre.xlsx
@@ -627,7 +627,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>-1,69</t>
+          <t>-0,9</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -647,7 +647,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>-26,83%</t>
+          <t>-17,32%</t>
         </is>
       </c>
     </row>
@@ -660,42 +660,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-2,42; 2,76</t>
+          <t>-2,65; 3,06</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-3,83; 4,78</t>
+          <t>-4,17; 5,11</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>1,51; 9,45</t>
+          <t>1,87; 9,53</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-7,93; 1,49</t>
+          <t>-4,71; 1,72</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-71,05; 197,11</t>
+          <t>-66,76; 263,62</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-45,5; 126,86</t>
+          <t>-48,2; 129,72</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>20,35; 535,7</t>
+          <t>42,45; 556,81</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-72,6; 35,48</t>
+          <t>-61,96; 51,83</t>
         </is>
       </c>
     </row>
@@ -727,7 +727,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>0,78</t>
+          <t>0,71</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -747,7 +747,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>30,15%</t>
+          <t>28,06%</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-1,86; 2,64</t>
+          <t>-2,02; 2,49</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-2,2; 3,84</t>
+          <t>-2,3; 3,77</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-2,26; 1,12</t>
+          <t>-2,27; 1,12</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-1,57; 2,58</t>
+          <t>-1,3; 2,42</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-39,46; 118,85</t>
+          <t>-44,59; 104,19</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-34,74; 96,67</t>
+          <t>-33,45; 100,79</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-70,0; 114,44</t>
+          <t>-73,03; 91,7</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-43,36; 172,96</t>
+          <t>-38,55; 151,03</t>
         </is>
       </c>
     </row>
@@ -827,7 +827,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>5,48</t>
+          <t>5,64</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -847,7 +847,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>51,92%</t>
+          <t>52,37%</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-0,03; 4,71</t>
+          <t>-0,05; 4,76</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-3,17; 3,4</t>
+          <t>-3,17; 3,65</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-1,95; 2,34</t>
+          <t>-2,13; 2,22</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0,96; 9,73</t>
+          <t>1,57; 10,06</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-23,32; 676,7</t>
+          <t>-31,13; 617,64</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-60,79; 170,13</t>
+          <t>-56,32; 194,89</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-70,83; 313,8</t>
+          <t>-74,97; 361,81</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>6,22; 111,78</t>
+          <t>12,0; 122,83</t>
         </is>
       </c>
     </row>
@@ -927,7 +927,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>1,76</t>
+          <t>3,53</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -947,7 +947,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>28,47%</t>
+          <t>55,99%</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-0,22; 4,7</t>
+          <t>-0,29; 4,66</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>2,54; 9,01</t>
+          <t>2,25; 8,94</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-0,48; 7,33</t>
+          <t>-0,22; 7,1</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-2,51; 5,3</t>
+          <t>-0,45; 6,41</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-16,64; 485,35</t>
+          <t>-15,67; 462,1</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>36,42; 792,98</t>
+          <t>45,2; 706,42</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-11,22; 227,33</t>
+          <t>-4,55; 243,22</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-30,26; 116,99</t>
+          <t>-5,59; 138,87</t>
         </is>
       </c>
     </row>
@@ -1027,7 +1027,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>7,62</t>
+          <t>7,57</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1047,7 +1047,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>56,73%</t>
+          <t>60,54%</t>
         </is>
       </c>
     </row>
@@ -1060,42 +1060,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-0,7; 5,86</t>
+          <t>-0,98; 5,58</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-6,27; 3,91</t>
+          <t>-5,83; 4,34</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-0,99; 5,06</t>
+          <t>-1,0; 4,81</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>2,15; 13,0</t>
+          <t>2,75; 12,54</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-48,52; 811,98</t>
+          <t>-47,79; 730,9</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-57,79; 73,53</t>
+          <t>-58,2; 80,9</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-61,0; 948,38</t>
+          <t>-58,12; —</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>12,12; 117,04</t>
+          <t>18,69; 126,62</t>
         </is>
       </c>
     </row>
@@ -1127,7 +1127,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>1,98</t>
+          <t>2,2</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1147,7 +1147,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>14,21%</t>
+          <t>16,1%</t>
         </is>
       </c>
     </row>
@@ -1160,42 +1160,42 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-0,39; 5,4</t>
+          <t>-0,34; 5,79</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-5,03; 2,24</t>
+          <t>-4,93; 1,94</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-3,47; 2,09</t>
+          <t>-3,5; 2,05</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-2,51; 6,61</t>
+          <t>-2,5; 6,57</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-28,79; 717,37</t>
+          <t>-28,82; 732,71</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-66,21; 75,02</t>
+          <t>-67,83; 71,81</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-77,65; 143,03</t>
+          <t>-78,58; 119,4</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-14,69; 58,84</t>
+          <t>-15,8; 56,3</t>
         </is>
       </c>
     </row>
@@ -1227,7 +1227,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>0,77</t>
+          <t>3,02</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1247,7 +1247,7 @@
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>13,36%</t>
+          <t>51,39%</t>
         </is>
       </c>
     </row>
@@ -1260,42 +1260,42 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-0,73; 3,64</t>
+          <t>-0,5; 3,76</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-0,76; 4,34</t>
+          <t>-0,69; 4,1</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-1,37; 3,47</t>
+          <t>-1,3; 3,61</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-3,49; 3,83</t>
+          <t>0,59; 5,26</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-21,33; 174,99</t>
+          <t>-13,56; 181,15</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-19,79; 167,37</t>
+          <t>-13,72; 182,03</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-29,25; 128,39</t>
+          <t>-25,92; 130,91</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-49,92; 75,73</t>
+          <t>6,72; 112,58</t>
         </is>
       </c>
     </row>
@@ -1327,7 +1327,7 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>0,38</t>
+          <t>-0,43</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -1347,7 +1347,7 @@
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>14,08%</t>
+          <t>-12,38%</t>
         </is>
       </c>
     </row>
@@ -1360,42 +1360,42 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-2,42; 0,76</t>
+          <t>-2,34; 1,0</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-0,66; 3,2</t>
+          <t>-0,59; 3,15</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-1,11; 2,52</t>
+          <t>-1,18; 2,39</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-1,32; 2,5</t>
+          <t>-1,89; 1,01</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-61,33; 39,81</t>
+          <t>-60,58; 54,1</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-20,34; 174,97</t>
+          <t>-18,49; 164,31</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-34,27; 133,97</t>
+          <t>-36,12; 138,66</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-34,03; 158,23</t>
+          <t>-44,98; 38,42</t>
         </is>
       </c>
     </row>
@@ -1427,7 +1427,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>1,82</t>
+          <t>2,14</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -1447,7 +1447,7 @@
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>30,17%</t>
+          <t>34,27%</t>
         </is>
       </c>
     </row>
@@ -1460,42 +1460,42 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>0,08; 1,82</t>
+          <t>0,08; 1,73</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>0,2; 2,36</t>
+          <t>0,18; 2,23</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>0,18; 1,95</t>
+          <t>0,22; 2,11</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>0,16; 3,36</t>
+          <t>1,01; 3,09</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>1,76; 85,31</t>
+          <t>1,07; 74,04</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>4,07; 66,76</t>
+          <t>3,62; 60,8</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>4,94; 77,86</t>
+          <t>6,52; 85,27</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>3,32; 67,03</t>
+          <t>15,02; 54,54</t>
         </is>
       </c>
     </row>
